--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2023_araucania.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2023_araucania.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="Total_Regional" sheetId="1" r:id="rId1"/>
     <sheet name="Por_Sexo" sheetId="2" r:id="rId2"/>
-    <sheet name="Por_Edad" sheetId="3" r:id="rId3"/>
+    <sheet name="Por_Prov" sheetId="3" r:id="rId3"/>
+    <sheet name="Por_Edad" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -353,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -364,19 +365,44 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Residentes</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Proyectada</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Cobertura</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Categoria_lbl</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Total
-Regional</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B2">
+        <v>1094085</v>
+      </c>
+      <c r="C2">
+        <v>1028201</v>
+      </c>
+      <c r="D2">
         <v>106.4076965496046</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -465,7 +491,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -476,7 +502,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Tramo_Edad</t>
+          <t>Provincia</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -503,17 +529,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0-14</t>
+          <t>Malleco</t>
         </is>
       </c>
       <c r="C2">
-        <v>194819</v>
+        <v>233014</v>
       </c>
       <c r="D2">
-        <v>198358</v>
+        <v>216169</v>
       </c>
       <c r="E2">
-        <v>98.21585214611964</v>
+        <v>107.7925141902863</v>
       </c>
     </row>
     <row r="3">
@@ -524,17 +550,96 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15-29</t>
+          <t>Cautín</t>
         </is>
       </c>
       <c r="C3">
-        <v>223930</v>
+        <v>861071</v>
       </c>
       <c r="D3">
-        <v>205052</v>
+        <v>812032</v>
       </c>
       <c r="E3">
-        <v>109.2064451943897</v>
+        <v>106.0390477222573</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Desagregación 1</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Tramo_Edad</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Residentes</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Proyectada</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Cobertura</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>50197</v>
+      </c>
+      <c r="D2">
+        <v>59411</v>
+      </c>
+      <c r="E2">
+        <v>84.49108750904715</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>5-9</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>69795</v>
+      </c>
+      <c r="D3">
+        <v>67442</v>
+      </c>
+      <c r="E3">
+        <v>103.4889238160197</v>
       </c>
     </row>
     <row r="4">
@@ -545,17 +650,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30-44</t>
+          <t>10-14</t>
         </is>
       </c>
       <c r="C4">
-        <v>235548</v>
+        <v>74827</v>
       </c>
       <c r="D4">
-        <v>214177</v>
+        <v>71505</v>
       </c>
       <c r="E4">
-        <v>109.97819560457</v>
+        <v>104.6458289630096</v>
       </c>
     </row>
     <row r="5">
@@ -566,17 +671,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45-64</t>
+          <t>15-19</t>
         </is>
       </c>
       <c r="C5">
-        <v>272743</v>
+        <v>73058</v>
       </c>
       <c r="D5">
-        <v>256026</v>
+        <v>66624</v>
       </c>
       <c r="E5">
-        <v>106.529414981291</v>
+        <v>109.6571805955812</v>
       </c>
     </row>
     <row r="6">
@@ -587,17 +692,269 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>65+</t>
+          <t>20-24</t>
         </is>
       </c>
       <c r="C6">
-        <v>167045</v>
+        <v>72043</v>
       </c>
       <c r="D6">
-        <v>154588</v>
+        <v>66314</v>
       </c>
       <c r="E6">
-        <v>108.0581933914663</v>
+        <v>108.6392013752752</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>25-29</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>78829</v>
+      </c>
+      <c r="D7">
+        <v>72114</v>
+      </c>
+      <c r="E7">
+        <v>109.3116454502593</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30-34</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>86497</v>
+      </c>
+      <c r="D8">
+        <v>76345</v>
+      </c>
+      <c r="E8">
+        <v>113.2975309450521</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>35-39</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>76442</v>
+      </c>
+      <c r="D9">
+        <v>68656</v>
+      </c>
+      <c r="E9">
+        <v>111.3405965975297</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>40-44</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>72609</v>
+      </c>
+      <c r="D10">
+        <v>69176</v>
+      </c>
+      <c r="E10">
+        <v>104.9627038279172</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>45-49</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>67990</v>
+      </c>
+      <c r="D11">
+        <v>68601</v>
+      </c>
+      <c r="E11">
+        <v>99.10934242941065</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>50-54</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>71642</v>
+      </c>
+      <c r="D12">
+        <v>65521</v>
+      </c>
+      <c r="E12">
+        <v>109.3420430091116</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>55-59</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>69967</v>
+      </c>
+      <c r="D13">
+        <v>64940</v>
+      </c>
+      <c r="E13">
+        <v>107.740991684632</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>60-64</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>63144</v>
+      </c>
+      <c r="D14">
+        <v>56964</v>
+      </c>
+      <c r="E14">
+        <v>110.8489572361491</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>65-69</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>52889</v>
+      </c>
+      <c r="D15">
+        <v>49451</v>
+      </c>
+      <c r="E15">
+        <v>106.9523366564882</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>70-74</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>40613</v>
+      </c>
+      <c r="D16">
+        <v>38319</v>
+      </c>
+      <c r="E16">
+        <v>105.9865862887862</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>75-79</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>31107</v>
+      </c>
+      <c r="D17">
+        <v>28110</v>
+      </c>
+      <c r="E17">
+        <v>110.6616862326574</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>80+</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>42436</v>
+      </c>
+      <c r="D18">
+        <v>38708</v>
+      </c>
+      <c r="E18">
+        <v>109.6310840136406</v>
       </c>
     </row>
   </sheetData>
